--- a/annotators/team/tg/annotated/abcnews.199762.xlsx
+++ b/annotators/team/tg/annotated/abcnews.199762.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\annotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C6D425-116D-4503-B5BA-703D18F71E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAFFE03-6E48-4B04-9402-1838CE2373FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="380">
   <si>
     <t>ID</t>
   </si>
@@ -1040,9 +1040,6 @@
     <t>sender_kgo</t>
   </si>
   <si>
-    <t>job_koch</t>
-  </si>
-  <si>
     <t>boston</t>
   </si>
   <si>
@@ -1118,15 +1115,9 @@
     <t>parser error: Artikel</t>
   </si>
   <si>
-    <t>zusätzliche ID, weil auto ref</t>
-  </si>
-  <si>
     <t>zusätzlich ref weil auto ref</t>
   </si>
   <si>
-    <t>alternativ: kein Ref, weil substantiviertes Verb</t>
-  </si>
-  <si>
     <t>treppenhaus_mall</t>
   </si>
   <si>
@@ -1145,13 +1136,31 @@
     <t>TYPE</t>
   </si>
   <si>
-    <t>IN FOCUS, weil im gleichen Satz referenziert?</t>
-  </si>
-  <si>
     <t>bridging: das police department ermittelt</t>
   </si>
   <si>
-    <t>in 209 + 213 konkret benannt; CHECK IS</t>
+    <t>BOUND</t>
+  </si>
+  <si>
+    <t>leichnam_frank</t>
+  </si>
+  <si>
+    <t>OLD</t>
+  </si>
+  <si>
+    <t>job_frank</t>
+  </si>
+  <si>
+    <t>parser error: nicht annotiert</t>
+  </si>
+  <si>
+    <t>kein CB, weil nicht im vorherherigen Satz explizit erwähnt</t>
+  </si>
+  <si>
+    <t>in 209 + 213 konkret benannt</t>
+  </si>
+  <si>
+    <t>Telegrammstil, eigentlich "Mall in SF"</t>
   </si>
 </sst>
 </file>
@@ -2281,7 +2290,8 @@
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="3.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" customWidth="1"/>
     <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="40.6640625" customWidth="1"/>
@@ -2494,7 +2504,7 @@
         <v>NEW</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H7" s="23" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2513,7 +2523,7 @@
         <v/>
       </c>
       <c r="L7" s="25" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -2581,7 +2591,7 @@
         <v/>
       </c>
       <c r="L9" s="25" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -2780,7 +2790,7 @@
         <v>OLD</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H17" s="23" t="s">
         <v>88</v>
@@ -2847,9 +2857,8 @@
         <v>98</v>
       </c>
       <c r="E19" s="27"/>
-      <c r="F19" s="28" t="str">
-        <f>IF(OR(E19="",E19="!!!"),"",IF(NOT(ISNA(VLOOKUP(E19,E$1:E18,1,FALSE()))),"OLD",IF(AND(E19&lt;&gt;"",E19&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+      <c r="F19" s="28" t="s">
+        <v>372</v>
       </c>
       <c r="G19" s="22" t="str">
         <f>IF(OR(E19="",E19="!!!"),"",IF(OR(J19=0,AND(J19=1,K19=1),AND(J19=1,I19="SBJ"),AND(J19=1,I19=0)),"?IN_FOCUS",IF(J19&lt;=2,"?ACTIVATED",IF(J19&lt;&gt;"","?FAMILIAR",IF(F19="NEW",IF(ISNA(VLOOKUP(E19,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -2872,7 +2881,7 @@
         <v/>
       </c>
       <c r="L19" s="29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -3004,7 +3013,7 @@
         <v>OLD</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H23" s="23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3276,14 +3285,14 @@
         <v>98</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F31" s="28" t="str">
         <f>IF(OR(E31="",E31="!!!"),"",IF(NOT(ISNA(VLOOKUP(E31,E$1:E30,1,FALSE()))),"OLD",IF(AND(E31&lt;&gt;"",E31&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H31" s="23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3389,7 +3398,7 @@
         <v>OLD</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H34" s="23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3677,7 +3686,7 @@
         <v>OLD</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H44" s="23" t="s">
         <v>88</v>
@@ -3841,7 +3850,7 @@
         <v>OLD</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H49" s="23" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4080,7 +4089,7 @@
         <v>OLD</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H56" s="23" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4408,7 +4417,7 @@
         <v>OLD</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H66" s="23" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4670,7 +4679,7 @@
         <v>331</v>
       </c>
       <c r="G76" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H76" s="23" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4835,7 +4844,7 @@
         <v>OLD</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H81" s="23" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -4854,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="29" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -4902,29 +4911,27 @@
         <v>98</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>326</v>
+        <v>373</v>
       </c>
       <c r="F83" s="28" t="str">
         <f>IF(OR(E83="",E83="!!!"),"",IF(NOT(ISNA(VLOOKUP(E83,E$1:E82,1,FALSE()))),"OLD",IF(AND(E83&lt;&gt;"",E83&lt;&gt;"!!!"),"NEW","")))</f>
-        <v>OLD</v>
+        <v>NEW</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="H83" s="23" t="s">
-        <v>88</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="H83" s="23"/>
       <c r="I83" s="24" t="str">
         <f>IF(OR(E83="",E83="!!!",F83="NEW"),"",INDEX(B$2:B82,-1+SUMPRODUCT(MAX(ROW(E$2:E82)*(E83=E$2:E82)))))</f>
-        <v>other_2</v>
-      </c>
-      <c r="J83" s="24">
+        <v/>
+      </c>
+      <c r="J83" s="24" t="str">
         <f ca="1">IF(OR(E83="",E83="!!!",F83="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E83)*(E83=E$2:E83)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E82)*(E2=E$1:E82))))))</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="24">
-        <f ca="1">IF(OR(E83="",E83="!!!",F83="NEW"),"",INDEX(J$1:J82,SUMPRODUCT(MAX(ROW(E$1:E82)*(E83=E$1:E82)))))</f>
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="K83" s="24" t="str">
+        <f>IF(OR(E83="",E83="!!!",F83="NEW"),"",INDEX(J$1:J82,SUMPRODUCT(MAX(ROW(E$1:E82)*(E83=E$1:E82)))))</f>
+        <v/>
       </c>
       <c r="L83" s="29"/>
     </row>
@@ -5133,29 +5140,29 @@
       <c r="D90" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E90" s="27"/>
+      <c r="E90" s="27" t="s">
+        <v>326</v>
+      </c>
       <c r="F90" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="G90" s="22" t="str">
-        <f>IF(OR(E90="",E90="!!!"),"",IF(OR(J90=0,AND(J90=1,K90=1),AND(J90=1,I90="SBJ"),AND(J90=1,I90=0)),"?IN_FOCUS",IF(J90&lt;=2,"?ACTIVATED",IF(J90&lt;&gt;"","?FAMILIAR",IF(F90="NEW",IF(ISNA(VLOOKUP(E90,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
-      </c>
-      <c r="H90" s="23" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
+        <v>374</v>
+      </c>
+      <c r="G90" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="H90" s="23" t="s">
+        <v>88</v>
       </c>
       <c r="I90" s="24" t="str">
         <f>IF(OR(E90="",E90="!!!",F90="NEW"),"",INDEX(B$2:B89,-1+SUMPRODUCT(MAX(ROW(E$2:E89)*(E90=E$2:E89)))))</f>
-        <v/>
-      </c>
-      <c r="J90" s="24" t="str">
+        <v>other_2</v>
+      </c>
+      <c r="J90" s="24">
         <f ca="1">IF(OR(E90="",E90="!!!",F90="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E90)*(E90=E$2:E90)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E89)*(E2=E$1:E89))))))</f>
-        <v/>
-      </c>
-      <c r="K90" s="24" t="str">
-        <f>IF(OR(E90="",E90="!!!",F90="NEW"),"",INDEX(J$1:J89,SUMPRODUCT(MAX(ROW(E$1:E89)*(E90=E$1:E89)))))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="24">
+        <f ca="1">IF(OR(E90="",E90="!!!",F90="NEW"),"",INDEX(J$1:J89,SUMPRODUCT(MAX(ROW(E$1:E89)*(E90=E$1:E89)))))</f>
+        <v>0</v>
       </c>
       <c r="L90" s="29"/>
     </row>
@@ -5242,7 +5249,7 @@
         <v>OLD</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H93" s="23" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5469,7 +5476,7 @@
         <v>NEW</v>
       </c>
       <c r="G100" s="22" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H100" s="23" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5541,7 +5548,7 @@
         <v>OLD</v>
       </c>
       <c r="G102" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H102" s="23" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -5559,9 +5566,7 @@
         <f ca="1">IF(OR(E102="",E102="!!!",F102="NEW"),"",INDEX(J$1:J101,SUMPRODUCT(MAX(ROW(E$1:E101)*(E102=E$1:E101)))))</f>
         <v>0</v>
       </c>
-      <c r="L102" s="29" t="s">
-        <v>374</v>
-      </c>
+      <c r="L102" s="29"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -5713,7 +5718,7 @@
         <v>OLD</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H109" s="23" t="s">
         <v>88</v>
@@ -5731,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="29" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -5808,7 +5813,7 @@
         <v>NEW</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H112" s="23" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5827,7 +5832,7 @@
         <v/>
       </c>
       <c r="L112" s="29" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -5975,7 +5980,7 @@
         <v>NEW</v>
       </c>
       <c r="G117" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H117" s="23" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6208,7 +6213,7 @@
         <v>NEW</v>
       </c>
       <c r="G124" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H124" s="23" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6227,7 +6232,7 @@
         <v/>
       </c>
       <c r="L124" s="29" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -6307,7 +6312,7 @@
       </c>
       <c r="E127" s="27"/>
       <c r="F127" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G127" s="22" t="str">
         <f>IF(OR(E127="",E127="!!!"),"",IF(OR(J127=0,AND(J127=1,K127=1),AND(J127=1,I127="SBJ"),AND(J127=1,I127=0)),"?IN_FOCUS",IF(J127&lt;=2,"?ACTIVATED",IF(J127&lt;&gt;"","?FAMILIAR",IF(F127="NEW",IF(ISNA(VLOOKUP(E127,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -6329,9 +6334,7 @@
         <f>IF(OR(E127="",E127="!!!",F127="NEW"),"",INDEX(J$1:J126,SUMPRODUCT(MAX(ROW(E$1:E126)*(E127=E$1:E126)))))</f>
         <v/>
       </c>
-      <c r="L127" s="29" t="s">
-        <v>367</v>
-      </c>
+      <c r="L127" s="29"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -6452,7 +6455,7 @@
         <v>OLD</v>
       </c>
       <c r="G133" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H133" s="23" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -6524,14 +6527,12 @@
         <v>OLD</v>
       </c>
       <c r="G135" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="H135" s="23" t="s">
-        <v>88</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="H135" s="23"/>
       <c r="I135" s="24" t="str">
         <f>IF(OR(E135="",E135="!!!",F135="NEW"),"",INDEX(B$2:B134,-1+SUMPRODUCT(MAX(ROW(E$2:E134)*(E135=E$2:E134)))))</f>
-        <v>SBJ</v>
+        <v>other</v>
       </c>
       <c r="J135" s="24">
         <f ca="1">IF(OR(E135="",E135="!!!",F135="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E135)*(E135=E$2:E135)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E134)*(E2=E$1:E134))))))</f>
@@ -6541,7 +6542,9 @@
         <f ca="1">IF(OR(E135="",E135="!!!",F135="NEW"),"",INDEX(J$1:J134,SUMPRODUCT(MAX(ROW(E$1:E134)*(E135=E$1:E134)))))</f>
         <v>0</v>
       </c>
-      <c r="L135" s="29"/>
+      <c r="L135" s="29" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -6776,7 +6779,7 @@
         <v/>
       </c>
       <c r="L142" s="29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -6903,7 +6906,7 @@
         <v>OLD</v>
       </c>
       <c r="G146" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H146" s="23" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -7068,7 +7071,7 @@
         <v>OLD</v>
       </c>
       <c r="G151" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H151" s="23" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -7228,16 +7231,11 @@
       <c r="D156" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E156" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="F156" s="28" t="str">
-        <f>IF(OR(E156="",E156="!!!"),"",IF(NOT(ISNA(VLOOKUP(E156,E$1:E155,1,FALSE()))),"OLD",IF(AND(E156&lt;&gt;"",E156&lt;&gt;"!!!"),"NEW","")))</f>
-        <v>NEW</v>
-      </c>
-      <c r="G156" s="22" t="s">
-        <v>370</v>
-      </c>
+      <c r="E156" s="27"/>
+      <c r="F156" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="G156" s="22"/>
       <c r="H156" s="23" t="str">
         <f t="shared" ca="1" si="8"/>
         <v/>
@@ -7301,14 +7299,14 @@
         <v>98</v>
       </c>
       <c r="E158" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F158" s="28" t="str">
         <f>IF(OR(E158="",E158="!!!"),"",IF(NOT(ISNA(VLOOKUP(E158,E$1:E157,1,FALSE()))),"OLD",IF(AND(E158&lt;&gt;"",E158&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G158" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H158" s="23" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -7532,7 +7530,7 @@
         <v>OLD</v>
       </c>
       <c r="G165" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H165" s="23" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -7551,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
@@ -7564,14 +7562,15 @@
       <c r="C166" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="E166" s="27"/>
+      <c r="E166" s="27" t="s">
+        <v>375</v>
+      </c>
       <c r="F166" s="28" t="str">
         <f>IF(OR(E166="",E166="!!!"),"",IF(NOT(ISNA(VLOOKUP(E166,E$1:E165,1,FALSE()))),"OLD",IF(AND(E166&lt;&gt;"",E166&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
-      </c>
-      <c r="G166" s="22" t="str">
-        <f>IF(OR(E166="",E166="!!!"),"",IF(OR(J166=0,AND(J166=1,K166=1),AND(J166=1,I166="SBJ"),AND(J166=1,I166=0)),"?IN_FOCUS",IF(J166&lt;=2,"?ACTIVATED",IF(J166&lt;&gt;"","?FAMILIAR",IF(F166="NEW",IF(ISNA(VLOOKUP(E166,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v/>
+        <v>NEW</v>
+      </c>
+      <c r="G166" s="22" t="s">
+        <v>368</v>
       </c>
       <c r="H166" s="23" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -7589,7 +7588,9 @@
         <f>IF(OR(E166="",E166="!!!",F166="NEW"),"",INDEX(J$1:J165,SUMPRODUCT(MAX(ROW(E$1:E165)*(E166=E$1:E165)))))</f>
         <v/>
       </c>
-      <c r="L166" s="29"/>
+      <c r="L166" s="29" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
@@ -7632,30 +7633,26 @@
       <c r="C168" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E168" s="27" t="s">
-        <v>339</v>
-      </c>
+      <c r="E168" s="27"/>
       <c r="F168" s="28" t="str">
         <f>IF(OR(E168="",E168="!!!"),"",IF(NOT(ISNA(VLOOKUP(E168,E$1:E167,1,FALSE()))),"OLD",IF(AND(E168&lt;&gt;"",E168&lt;&gt;"!!!"),"NEW","")))</f>
-        <v>OLD</v>
-      </c>
-      <c r="G168" s="22" t="s">
-        <v>369</v>
-      </c>
+        <v/>
+      </c>
+      <c r="G168" s="22"/>
       <c r="H168" s="23" t="str">
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
       <c r="I168" s="24" t="str">
         <f>IF(OR(E168="",E168="!!!",F168="NEW"),"",INDEX(B$2:B167,-1+SUMPRODUCT(MAX(ROW(E$2:E167)*(E168=E$2:E167)))))</f>
-        <v>other_4</v>
-      </c>
-      <c r="J168" s="24">
+        <v/>
+      </c>
+      <c r="J168" s="24" t="str">
         <f ca="1">IF(OR(E168="",E168="!!!",F168="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E168)*(E168=E$2:E168)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E167)*(E2=E$1:E167))))))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="K168" s="24" t="str">
-        <f ca="1">IF(OR(E168="",E168="!!!",F168="NEW"),"",INDEX(J$1:J167,SUMPRODUCT(MAX(ROW(E$1:E167)*(E168=E$1:E167)))))</f>
+        <f>IF(OR(E168="",E168="!!!",F168="NEW"),"",INDEX(J$1:J167,SUMPRODUCT(MAX(ROW(E$1:E167)*(E168=E$1:E167)))))</f>
         <v/>
       </c>
       <c r="L168" s="29"/>
@@ -7736,7 +7733,7 @@
         <v>98</v>
       </c>
       <c r="E171" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F171" s="28" t="str">
         <f>IF(OR(E171="",E171="!!!"),"",IF(NOT(ISNA(VLOOKUP(E171,E$1:E170,1,FALSE()))),"OLD",IF(AND(E171&lt;&gt;"",E171&lt;&gt;"!!!"),"NEW","")))</f>
@@ -7762,7 +7759,7 @@
         <v/>
       </c>
       <c r="L171" s="29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -7835,7 +7832,7 @@
         <v/>
       </c>
       <c r="L173" s="29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -7927,7 +7924,7 @@
         <v>OLD</v>
       </c>
       <c r="G176" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H176" s="23" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -8152,7 +8149,7 @@
         <v>98</v>
       </c>
       <c r="E185" s="27" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F185" s="28" t="str">
         <f>IF(OR(E185="",E185="!!!"),"",IF(NOT(ISNA(VLOOKUP(E185,E$1:E184,1,FALSE()))),"OLD",IF(AND(E185&lt;&gt;"",E185&lt;&gt;"!!!"),"NEW","")))</f>
@@ -8224,14 +8221,14 @@
         <v>98</v>
       </c>
       <c r="E187" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F187" s="28" t="str">
         <f>IF(OR(E187="",E187="!!!"),"",IF(NOT(ISNA(VLOOKUP(E187,E$1:E186,1,FALSE()))),"OLD",IF(AND(E187&lt;&gt;"",E187&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G187" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H187" s="23" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -8429,10 +8426,10 @@
         <v>98</v>
       </c>
       <c r="E193" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="F193" s="28" t="s">
         <v>343</v>
-      </c>
-      <c r="F193" s="28" t="s">
-        <v>344</v>
       </c>
       <c r="G193" s="22" t="s">
         <v>86</v>
@@ -8454,7 +8451,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L193" s="29" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
@@ -8500,7 +8497,7 @@
         <v>OLD</v>
       </c>
       <c r="G195" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H195" s="23" t="s">
         <v>88</v>
@@ -8537,7 +8534,7 @@
         <v>OLD</v>
       </c>
       <c r="G196" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H196" s="23" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -8727,7 +8724,7 @@
       </c>
       <c r="E202" s="27"/>
       <c r="F202" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G202" s="22" t="str">
         <f>IF(OR(E202="",E202="!!!"),"",IF(OR(J202=0,AND(J202=1,K202=1),AND(J202=1,I202="SBJ"),AND(J202=1,I202=0)),"?IN_FOCUS",IF(J202&lt;=2,"?ACTIVATED",IF(J202&lt;&gt;"","?FAMILIAR",IF(F202="NEW",IF(ISNA(VLOOKUP(E202,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -8956,14 +8953,14 @@
         <v>98</v>
       </c>
       <c r="E211" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F211" s="28" t="str">
         <f>IF(OR(E211="",E211="!!!"),"",IF(NOT(ISNA(VLOOKUP(E211,E$1:E210,1,FALSE()))),"OLD",IF(AND(E211&lt;&gt;"",E211&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G211" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H211" s="23" t="s">
         <v>88</v>
@@ -9086,9 +9083,7 @@
         <v>128</v>
       </c>
       <c r="E215" s="27"/>
-      <c r="F215" s="28" t="s">
-        <v>332</v>
-      </c>
+      <c r="F215" s="28"/>
       <c r="G215" s="22" t="str">
         <f>IF(OR(E215="",E215="!!!"),"",IF(OR(J215=0,AND(J215=1,K215=1),AND(J215=1,I215="SBJ"),AND(J215=1,I215=0)),"?IN_FOCUS",IF(J215&lt;=2,"?ACTIVATED",IF(J215&lt;&gt;"","?FAMILIAR",IF(F215="NEW",IF(ISNA(VLOOKUP(E215,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
         <v/>
@@ -9156,9 +9151,8 @@
         <v>98</v>
       </c>
       <c r="E217" s="27"/>
-      <c r="F217" s="28" t="str">
-        <f>IF(OR(E217="",E217="!!!"),"",IF(NOT(ISNA(VLOOKUP(E217,E$1:E216,1,FALSE()))),"OLD",IF(AND(E217&lt;&gt;"",E217&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+      <c r="F217" s="28" t="s">
+        <v>372</v>
       </c>
       <c r="G217" s="22" t="str">
         <f>IF(OR(E217="",E217="!!!"),"",IF(OR(J217=0,AND(J217=1,K217=1),AND(J217=1,I217="SBJ"),AND(J217=1,I217=0)),"?IN_FOCUS",IF(J217&lt;=2,"?ACTIVATED",IF(J217&lt;&gt;"","?FAMILIAR",IF(F217="NEW",IF(ISNA(VLOOKUP(E217,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -9181,7 +9175,7 @@
         <v/>
       </c>
       <c r="L217" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
@@ -9390,14 +9384,14 @@
         <v>98</v>
       </c>
       <c r="E224" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F224" s="28" t="str">
         <f>IF(OR(E224="",E224="!!!"),"",IF(NOT(ISNA(VLOOKUP(E224,E$1:E223,1,FALSE()))),"OLD",IF(AND(E224&lt;&gt;"",E224&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G224" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H224" s="23" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9689,14 +9683,14 @@
         <v>98</v>
       </c>
       <c r="E233" s="27" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F233" s="28" t="str">
         <f>IF(OR(E233="",E233="!!!"),"",IF(NOT(ISNA(VLOOKUP(E233,E$1:E232,1,FALSE()))),"OLD",IF(AND(E233&lt;&gt;"",E233&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G233" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H233" s="23" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9797,14 +9791,14 @@
         <v>98</v>
       </c>
       <c r="E238" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F238" s="28" t="str">
         <f>IF(OR(E238="",E238="!!!"),"",IF(NOT(ISNA(VLOOKUP(E238,E$1:E237,1,FALSE()))),"OLD",IF(AND(E238&lt;&gt;"",E238&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G238" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H238" s="23" t="str">
         <f t="shared" ref="H238:H253" ca="1" si="12">IF(J238&lt;&gt;1,"",IF(I238="SBJ","CB","?"))</f>
@@ -9835,14 +9829,14 @@
         <v>115</v>
       </c>
       <c r="E239" s="27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F239" s="28" t="str">
         <f>IF(OR(E239="",E239="!!!"),"",IF(NOT(ISNA(VLOOKUP(E239,E$1:E238,1,FALSE()))),"OLD",IF(AND(E239&lt;&gt;"",E239&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G239" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H239" s="23" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -9907,14 +9901,14 @@
         <v>98</v>
       </c>
       <c r="E241" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F241" s="28" t="str">
         <f>IF(OR(E241="",E241="!!!"),"",IF(NOT(ISNA(VLOOKUP(E241,E$1:E240,1,FALSE()))),"OLD",IF(AND(E241&lt;&gt;"",E241&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G241" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H241" s="23" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -9945,14 +9939,14 @@
         <v>115</v>
       </c>
       <c r="E242" s="27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F242" s="28" t="str">
         <f>IF(OR(E242="",E242="!!!"),"",IF(NOT(ISNA(VLOOKUP(E242,E$1:E241,1,FALSE()))),"OLD",IF(AND(E242&lt;&gt;"",E242&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G242" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H242" s="23" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -10073,7 +10067,7 @@
         <v/>
       </c>
       <c r="L245" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
@@ -10121,13 +10115,13 @@
         <v>98</v>
       </c>
       <c r="E247" s="27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F247" s="28" t="s">
         <v>331</v>
       </c>
       <c r="G247" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H247" s="23" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -10199,7 +10193,7 @@
         <v>OLD</v>
       </c>
       <c r="G249" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H249" s="23" t="s">
         <v>88</v>
@@ -10232,7 +10226,7 @@
         <v>98</v>
       </c>
       <c r="E250" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F250" s="28" t="str">
         <f>IF(OR(E250="",E250="!!!"),"",IF(NOT(ISNA(VLOOKUP(E250,E$1:E249,1,FALSE()))),"OLD",IF(AND(E250&lt;&gt;"",E250&lt;&gt;"!!!"),"NEW","")))</f>
@@ -10415,7 +10409,7 @@
         <v>OLD</v>
       </c>
       <c r="G257" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H257" s="23" t="str">
         <f t="shared" ref="H257:H281" ca="1" si="13">IF(J257&lt;&gt;1,"",IF(I257="SBJ","CB","?"))</f>
@@ -10611,7 +10605,7 @@
         <v>OLD</v>
       </c>
       <c r="G263" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H263" s="23" t="s">
         <v>88</v>
@@ -10961,7 +10955,7 @@
       </c>
       <c r="E274" s="27"/>
       <c r="F274" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G274" s="22" t="str">
         <f>IF(OR(E274="",E274="!!!"),"",IF(OR(J274=0,AND(J274=1,K274=1),AND(J274=1,I274="SBJ"),AND(J274=1,I274=0)),"?IN_FOCUS",IF(J274&lt;=2,"?ACTIVATED",IF(J274&lt;&gt;"","?FAMILIAR",IF(F274="NEW",IF(ISNA(VLOOKUP(E274,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -11037,7 +11031,7 @@
         <v>OLD</v>
       </c>
       <c r="G276" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H276" s="23" t="str">
         <f t="shared" ca="1" si="13"/>
@@ -11300,7 +11294,7 @@
         <v>OLD</v>
       </c>
       <c r="G286" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H286" s="23" t="s">
         <v>88</v>
@@ -11470,7 +11464,7 @@
         <v>OLD</v>
       </c>
       <c r="G291" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H291" s="23" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11703,7 +11697,7 @@
         <v>OLD</v>
       </c>
       <c r="G298" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H298" s="23" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11766,7 +11760,7 @@
         <v>OLD</v>
       </c>
       <c r="G300" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H300" s="23" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11785,7 +11779,7 @@
         <v/>
       </c>
       <c r="L300" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
@@ -11876,7 +11870,7 @@
         <v>OLD</v>
       </c>
       <c r="G305" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H305" s="23" t="s">
         <v>88</v>
@@ -11909,7 +11903,7 @@
         <v/>
       </c>
       <c r="H306" s="23" t="str">
-        <f t="shared" ref="H305:H323" ca="1" si="15">IF(J306&lt;&gt;1,"",IF(I306="SBJ","CB","?"))</f>
+        <f t="shared" ref="H306:H323" ca="1" si="15">IF(J306&lt;&gt;1,"",IF(I306="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I306" s="24" t="str">
@@ -12040,7 +12034,7 @@
         <v>OLD</v>
       </c>
       <c r="G310" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H310" s="23" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -12270,7 +12264,7 @@
         <v>OLD</v>
       </c>
       <c r="G317" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H317" s="23" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -12289,7 +12283,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
@@ -12341,7 +12335,7 @@
         <v>OLD</v>
       </c>
       <c r="G319" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H319" s="23" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -12511,7 +12505,7 @@
         <v>OLD</v>
       </c>
       <c r="G326" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H326" s="23" t="s">
         <v>88</v>
@@ -12544,7 +12538,7 @@
         <v/>
       </c>
       <c r="H327" s="23" t="str">
-        <f t="shared" ref="H326:H335" ca="1" si="16">IF(J327&lt;&gt;1,"",IF(I327="SBJ","CB","?"))</f>
+        <f t="shared" ref="H327:H335" ca="1" si="16">IF(J327&lt;&gt;1,"",IF(I327="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I327" s="24" t="str">
@@ -12869,7 +12863,7 @@
         <v>OLD</v>
       </c>
       <c r="G339" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H339" s="23" t="str">
         <f t="shared" ref="H339:H364" ca="1" si="17">IF(J339&lt;&gt;1,"",IF(I339="SBJ","CB","?"))</f>
@@ -12900,14 +12894,14 @@
         <v>205</v>
       </c>
       <c r="E340" s="27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F340" s="28" t="str">
         <f>IF(OR(E340="",E340="!!!"),"",IF(NOT(ISNA(VLOOKUP(E340,E$1:E339,1,FALSE()))),"OLD",IF(AND(E340&lt;&gt;"",E340&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G340" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H340" s="23" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -12970,7 +12964,7 @@
         <v>OLD</v>
       </c>
       <c r="G342" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H342" s="23" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -13001,14 +12995,14 @@
         <v>205</v>
       </c>
       <c r="E343" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F343" s="28" t="str">
         <f>IF(OR(E343="",E343="!!!"),"",IF(NOT(ISNA(VLOOKUP(E343,E$1:E342,1,FALSE()))),"OLD",IF(AND(E343&lt;&gt;"",E343&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G343" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H343" s="23" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -13159,7 +13153,7 @@
         <v/>
       </c>
       <c r="L347" s="29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
@@ -13207,14 +13201,14 @@
         <v>98</v>
       </c>
       <c r="E349" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F349" s="28" t="str">
         <f>IF(OR(E349="",E349="!!!"),"",IF(NOT(ISNA(VLOOKUP(E349,E$1:E348,1,FALSE()))),"OLD",IF(AND(E349&lt;&gt;"",E349&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G349" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H349" s="23" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -13409,14 +13403,14 @@
         <v>98</v>
       </c>
       <c r="E355" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F355" s="28" t="str">
         <f>IF(OR(E355="",E355="!!!"),"",IF(NOT(ISNA(VLOOKUP(E355,E$1:E354,1,FALSE()))),"OLD",IF(AND(E355&lt;&gt;"",E355&lt;&gt;"!!!"),"NEW","")))</f>
         <v>OLD</v>
       </c>
       <c r="G355" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H355" s="23" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -13505,7 +13499,7 @@
         <v/>
       </c>
       <c r="L357" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
@@ -13653,7 +13647,7 @@
         <v>OLD</v>
       </c>
       <c r="G362" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H362" s="23" t="s">
         <v>88</v>
@@ -13760,7 +13754,7 @@
         <v>OLD</v>
       </c>
       <c r="G367" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H367" s="23" t="s">
         <v>88</v>
@@ -13793,7 +13787,7 @@
         <v/>
       </c>
       <c r="H368" s="23" t="str">
-        <f t="shared" ref="H367:H376" ca="1" si="18">IF(J368&lt;&gt;1,"",IF(I368="SBJ","CB","?"))</f>
+        <f t="shared" ref="H368:H376" ca="1" si="18">IF(J368&lt;&gt;1,"",IF(I368="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I368" s="24" t="str">
@@ -14096,7 +14090,7 @@
         <v>OLD</v>
       </c>
       <c r="G379" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H379" s="23" t="s">
         <v>88</v>
@@ -14129,7 +14123,7 @@
         <v/>
       </c>
       <c r="H380" s="23" t="str">
-        <f t="shared" ref="H379:H389" ca="1" si="19">IF(J380&lt;&gt;1,"",IF(I380="SBJ","CB","?"))</f>
+        <f t="shared" ref="H380:H389" ca="1" si="19">IF(J380&lt;&gt;1,"",IF(I380="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I380" s="24" t="str">
@@ -14358,7 +14352,7 @@
       </c>
       <c r="E387" s="27"/>
       <c r="F387" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G387" s="22" t="str">
         <f>IF(OR(E387="",E387="!!!"),"",IF(OR(J387=0,AND(J387=1,K387=1),AND(J387=1,I387="SBJ"),AND(J387=1,I387=0)),"?IN_FOCUS",IF(J387&lt;=2,"?ACTIVATED",IF(J387&lt;&gt;"","?FAMILIAR",IF(F387="NEW",IF(ISNA(VLOOKUP(E387,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -14554,7 +14548,7 @@
       </c>
       <c r="E395" s="27"/>
       <c r="F395" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G395" s="22" t="str">
         <f>IF(OR(E395="",E395="!!!"),"",IF(OR(J395=0,AND(J395=1,K395=1),AND(J395=1,I395="SBJ"),AND(J395=1,I395=0)),"?IN_FOCUS",IF(J395&lt;=2,"?ACTIVATED",IF(J395&lt;&gt;"","?FAMILIAR",IF(F395="NEW",IF(ISNA(VLOOKUP(E395,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -14577,7 +14571,7 @@
         <v/>
       </c>
       <c r="L395" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.3">
@@ -14625,9 +14619,8 @@
         <v>98</v>
       </c>
       <c r="E397" s="27"/>
-      <c r="F397" s="28" t="str">
-        <f>IF(OR(E397="",E397="!!!"),"",IF(NOT(ISNA(VLOOKUP(E397,E$1:E396,1,FALSE()))),"OLD",IF(AND(E397&lt;&gt;"",E397&lt;&gt;"!!!"),"NEW","")))</f>
-        <v/>
+      <c r="F397" s="28" t="s">
+        <v>372</v>
       </c>
       <c r="G397" s="22" t="str">
         <f>IF(OR(E397="",E397="!!!"),"",IF(OR(J397=0,AND(J397=1,K397=1),AND(J397=1,I397="SBJ"),AND(J397=1,I397=0)),"?IN_FOCUS",IF(J397&lt;=2,"?ACTIVATED",IF(J397&lt;&gt;"","?FAMILIAR",IF(F397="NEW",IF(ISNA(VLOOKUP(E397,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -14650,7 +14643,7 @@
         <v/>
       </c>
       <c r="L397" s="29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.3">
@@ -14729,14 +14722,14 @@
         <v>98</v>
       </c>
       <c r="E400" s="27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F400" s="28" t="str">
         <f>IF(OR(E400="",E400="!!!"),"",IF(NOT(ISNA(VLOOKUP(E400,E$1:E399,1,FALSE()))),"OLD",IF(AND(E400&lt;&gt;"",E400&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G400" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H400" s="23" t="str">
         <f t="shared" ca="1" si="20"/>
@@ -14901,7 +14894,7 @@
         <v>OLD</v>
       </c>
       <c r="G405" s="22" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H405" s="23" t="s">
         <v>88</v>
@@ -14959,7 +14952,7 @@
         <v/>
       </c>
       <c r="L406" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.3">
@@ -15347,7 +15340,7 @@
         <v>OLD</v>
       </c>
       <c r="G418" s="22" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H418" s="23" t="str">
         <f t="shared" ca="1" si="20"/>
@@ -15421,7 +15414,7 @@
         <v/>
       </c>
       <c r="F422" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G422" s="22" t="str">
         <f>IF(OR(E422="",E422="!!!"),"",IF(OR(J422=0,AND(J422=1,K422=1),AND(J422=1,I422="SBJ"),AND(J422=1,I422=0)),"?IN_FOCUS",IF(J422&lt;=2,"?ACTIVATED",IF(J422&lt;&gt;"","?FAMILIAR",IF(F422="NEW",IF(ISNA(VLOOKUP(E422,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -15444,7 +15437,7 @@
         <v/>
       </c>
       <c r="L422" s="29" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.3">
@@ -15530,7 +15523,7 @@
       </c>
       <c r="E425" s="27"/>
       <c r="F425" s="28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G425" s="22" t="str">
         <f>IF(OR(E425="",E425="!!!"),"",IF(OR(J425=0,AND(J425=1,K425=1),AND(J425=1,I425="SBJ"),AND(J425=1,I425=0)),"?IN_FOCUS",IF(J425&lt;=2,"?ACTIVATED",IF(J425&lt;&gt;"","?FAMILIAR",IF(F425="NEW",IF(ISNA(VLOOKUP(E425,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
@@ -15649,7 +15642,7 @@
         <v>OLD</v>
       </c>
       <c r="G428" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H428" s="23" t="s">
         <v>88</v>
@@ -15858,14 +15851,14 @@
         <v>98</v>
       </c>
       <c r="E434" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F434" s="28" t="str">
         <f>IF(OR(E434="",E434="!!!"),"",IF(NOT(ISNA(VLOOKUP(E434,E$1:E433,1,FALSE()))),"OLD",IF(AND(E434&lt;&gt;"",E434&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G434" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H434" s="23" t="str">
         <f t="shared" ca="1" si="22"/>
@@ -15940,7 +15933,7 @@
         <v>OLD</v>
       </c>
       <c r="G436" s="22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H436" s="23" t="str">
         <f t="shared" ca="1" si="22"/>
@@ -16042,14 +16035,14 @@
         <v>98</v>
       </c>
       <c r="E439" s="27" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F439" s="28" t="str">
         <f>IF(OR(E439="",E439="!!!"),"",IF(NOT(ISNA(VLOOKUP(E439,E$1:E438,1,FALSE()))),"OLD",IF(AND(E439&lt;&gt;"",E439&lt;&gt;"!!!"),"NEW","")))</f>
         <v>NEW</v>
       </c>
       <c r="G439" s="22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H439" s="23" t="str">
         <f t="shared" ca="1" si="22"/>
